--- a/data/raw/TtR Legacy.xlsx
+++ b/data/raw/TtR Legacy.xlsx
@@ -12,6 +12,7 @@
     <sheet state="visible" name="Circus" sheetId="7" r:id="rId11"/>
     <sheet state="visible" name="timetable" sheetId="8" r:id="rId12"/>
     <sheet state="visible" name="Bankslips" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="map" sheetId="10" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2205" uniqueCount="267">
   <si>
     <t>id</t>
   </si>
@@ -748,6 +749,78 @@
   </si>
   <si>
     <t>missing</t>
+  </si>
+  <si>
+    <t>jigsaw</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>bridges</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>company</t>
+  </si>
+  <si>
+    <t>port</t>
+  </si>
+  <si>
+    <t>degree</t>
+  </si>
+  <si>
+    <t>calc</t>
+  </si>
+  <si>
+    <t>verfiy</t>
+  </si>
+  <si>
+    <t>Northeast</t>
+  </si>
+  <si>
+    <t>big</t>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>Atlantic Coast</t>
+  </si>
+  <si>
+    <t>The South</t>
+  </si>
+  <si>
+    <t>Mama O'Connel</t>
+  </si>
+  <si>
+    <t>gray</t>
+  </si>
+  <si>
+    <t>big city</t>
+  </si>
+  <si>
+    <t>Appalachia</t>
+  </si>
+  <si>
+    <t>charleston</t>
+  </si>
+  <si>
+    <t>Monterray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">green </t>
   </si>
 </sst>
 </file>
@@ -906,7 +979,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1025,6 +1098,15 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1084,7 +1166,7 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="9">
+  <tableStyles count="11">
     <tableStyle count="4" pivot="0" name="Tickets-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
@@ -1139,11 +1221,27 @@
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
+    <tableStyle count="4" pivot="0" name="map-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+    <tableStyle count="4" pivot="0" name="map-style 2">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
   </tableStyles>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1203,6 +1301,35 @@
     <tableColumn name="valid" id="15"/>
   </tableColumns>
   <tableStyleInfo name="Tickets-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F201" displayName="Table2" name="Table2" id="10">
+  <tableColumns count="6">
+    <tableColumn name="jigsaw" id="1"/>
+    <tableColumn name="to" id="2"/>
+    <tableColumn name="from" id="3"/>
+    <tableColumn name="length" id="4"/>
+    <tableColumn name="color" id="5"/>
+    <tableColumn name="bridges" id="6"/>
+  </tableColumns>
+  <tableStyleInfo name="map-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="H1:N64" displayName="cities" name="cities" id="11">
+  <tableColumns count="7">
+    <tableColumn name="jigsaw" id="1"/>
+    <tableColumn name="city" id="2"/>
+    <tableColumn name="company" id="3"/>
+    <tableColumn name="port" id="4"/>
+    <tableColumn name="degree" id="5"/>
+    <tableColumn name="calc" id="6"/>
+    <tableColumn name="verfiy" id="7"/>
+  </tableColumns>
+  <tableStyleInfo name="map-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -7996,6 +8123,5138 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1" ht="22.5" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F1" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="M1" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="N1" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="P1" s="4" t="str">
+        <f>if(AND(cities[verfiy]),"TRUE","FALSE")</f>
+        <v>TRUE</v>
+      </c>
+    </row>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2" s="42"/>
+      <c r="H2" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="M2" s="42">
+        <f>countif(Table2[[to]:[from]],I2)</f>
+        <v>4</v>
+      </c>
+      <c r="N2" s="42" t="b">
+        <f t="shared" ref="N2:N64" si="1">M2=L2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="F3" s="42"/>
+      <c r="H3" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="M3" s="42">
+        <f>countif(Table2[[to]:[from]],I3)</f>
+        <v>5</v>
+      </c>
+      <c r="N3" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="42"/>
+      <c r="H4" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M4" s="42">
+        <f>countif(Table2[[to]:[from]],I4)</f>
+        <v>8</v>
+      </c>
+      <c r="N4" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="F5" s="42"/>
+      <c r="H5" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="K5" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L5" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M5" s="42">
+        <f>countif(Table2[[to]:[from]],I5)</f>
+        <v>8</v>
+      </c>
+      <c r="N5" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F6" s="42"/>
+      <c r="H6" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="K6" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L6" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M6" s="42">
+        <f>countif(Table2[[to]:[from]],I6)</f>
+        <v>8</v>
+      </c>
+      <c r="N6" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F7" s="42"/>
+      <c r="H7" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="I7" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="K7" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L7" s="26">
+        <v>9.0</v>
+      </c>
+      <c r="M7" s="42">
+        <f>countif(Table2[[to]:[from]],I7)</f>
+        <v>9</v>
+      </c>
+      <c r="N7" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="H8" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="I8" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="M8" s="42">
+        <f>countif(Table2[[to]:[from]],I8)</f>
+        <v>4</v>
+      </c>
+      <c r="N8" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F9" s="42"/>
+      <c r="H9" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="I9" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M9" s="42">
+        <f>countif(Table2[[to]:[from]],I9)</f>
+        <v>8</v>
+      </c>
+      <c r="N9" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F10" s="42"/>
+      <c r="H10" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K10" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L10" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M10" s="42">
+        <f>countif(Table2[[to]:[from]],I10)</f>
+        <v>7</v>
+      </c>
+      <c r="N10" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F11" s="42"/>
+      <c r="H11" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="I11" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K11" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L11" s="26">
+        <v>6.0</v>
+      </c>
+      <c r="M11" s="42">
+        <f>countif(Table2[[to]:[from]],I11)</f>
+        <v>6</v>
+      </c>
+      <c r="N11" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="42"/>
+      <c r="H12" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="I12" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K12" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L12" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M12" s="42">
+        <f>countif(Table2[[to]:[from]],I12)</f>
+        <v>7</v>
+      </c>
+      <c r="N12" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F13" s="42"/>
+      <c r="H13" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K13" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L13" s="26">
+        <v>6.0</v>
+      </c>
+      <c r="M13" s="42">
+        <f>countif(Table2[[to]:[from]],I13)</f>
+        <v>6</v>
+      </c>
+      <c r="N13" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F14" s="42"/>
+      <c r="H14" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K14" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L14" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="M14" s="42">
+        <f>countif(Table2[[to]:[from]],I14)</f>
+        <v>4</v>
+      </c>
+      <c r="N14" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F15" s="42"/>
+      <c r="H15" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K15" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L15" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="M15" s="42">
+        <f>countif(Table2[[to]:[from]],I15)</f>
+        <v>4</v>
+      </c>
+      <c r="N15" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F16" s="42"/>
+      <c r="H16" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="K16" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M16" s="42">
+        <f>countif(Table2[[to]:[from]],I16)</f>
+        <v>8</v>
+      </c>
+      <c r="N16" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F17" s="42"/>
+      <c r="H17" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="K17" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="L17" s="26">
+        <v>6.0</v>
+      </c>
+      <c r="M17" s="42">
+        <f>countif(Table2[[to]:[from]],I17)</f>
+        <v>6</v>
+      </c>
+      <c r="N17" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F18" s="42"/>
+      <c r="H18" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="K18" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="L18" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M18" s="42">
+        <f>countif(Table2[[to]:[from]],I18)</f>
+        <v>7</v>
+      </c>
+      <c r="N18" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F19" s="42"/>
+      <c r="H19" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="K19" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="L19" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M19" s="42">
+        <f>countif(Table2[[to]:[from]],I19)</f>
+        <v>7</v>
+      </c>
+      <c r="N19" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F20" s="42"/>
+      <c r="H20" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="K20" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="M20" s="42">
+        <f>countif(Table2[[to]:[from]],I20)</f>
+        <v>4</v>
+      </c>
+      <c r="N20" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1">
+      <c r="A21" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F21" s="42"/>
+      <c r="H21" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="K21" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L21" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M21" s="42">
+        <f>countif(Table2[[to]:[from]],I21)</f>
+        <v>7</v>
+      </c>
+      <c r="N21" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F22" s="42"/>
+      <c r="H22" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="J22" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="K22" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L22" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M22" s="42">
+        <f>countif(Table2[[to]:[from]],I22)</f>
+        <v>8</v>
+      </c>
+      <c r="N22" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="A23" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F23" s="42"/>
+      <c r="H23" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="J23" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K23" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M23" s="42">
+        <f>countif(Table2[[to]:[from]],I23)</f>
+        <v>7</v>
+      </c>
+      <c r="N23" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="A24" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F24" s="42"/>
+      <c r="H24" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="K24" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L24" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M24" s="42">
+        <f>countif(Table2[[to]:[from]],I24)</f>
+        <v>7</v>
+      </c>
+      <c r="N24" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="A25" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F25" s="42"/>
+      <c r="H25" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J25" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="K25" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M25" s="42">
+        <f>countif(Table2[[to]:[from]],I25)</f>
+        <v>7</v>
+      </c>
+      <c r="N25" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="22.5" customHeight="1">
+      <c r="A26" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F26" s="42"/>
+      <c r="H26" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="I26" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="K26" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L26" s="26">
+        <v>6.0</v>
+      </c>
+      <c r="M26" s="42">
+        <f>countif(Table2[[to]:[from]],I26)</f>
+        <v>6</v>
+      </c>
+      <c r="N26" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F27" s="42"/>
+      <c r="H27" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="I27" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="J27" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="K27" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="26">
+        <v>10.0</v>
+      </c>
+      <c r="M27" s="42">
+        <f>countif(Table2[[to]:[from]],I27)</f>
+        <v>10</v>
+      </c>
+      <c r="N27" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="22.5" customHeight="1">
+      <c r="A28" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F28" s="42"/>
+      <c r="H28" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="I28" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="J28" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="K28" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M28" s="42">
+        <f>countif(Table2[[to]:[from]],I28)</f>
+        <v>8</v>
+      </c>
+      <c r="N28" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="22.5" customHeight="1">
+      <c r="A29" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F29" s="42"/>
+      <c r="H29" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="I29" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="J29" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="K29" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="26">
+        <v>6.0</v>
+      </c>
+      <c r="M29" s="42">
+        <f>countif(Table2[[to]:[from]],I29)</f>
+        <v>6</v>
+      </c>
+      <c r="N29" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" customHeight="1">
+      <c r="A30" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F30" s="42"/>
+      <c r="H30" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="I30" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J30" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K30" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L30" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="M30" s="42">
+        <f>countif(Table2[[to]:[from]],I30)</f>
+        <v>5</v>
+      </c>
+      <c r="N30" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" customHeight="1">
+      <c r="A31" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F31" s="42"/>
+      <c r="H31" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="I31" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="J31" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="K31" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L31" s="26">
+        <v>10.0</v>
+      </c>
+      <c r="M31" s="42">
+        <f>countif(Table2[[to]:[from]],I31)</f>
+        <v>10</v>
+      </c>
+      <c r="N31" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="22.5" customHeight="1">
+      <c r="A32" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F32" s="42"/>
+      <c r="H32" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="I32" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="J32" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="K32" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L32" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M32" s="42">
+        <f>countif(Table2[[to]:[from]],I32)</f>
+        <v>8</v>
+      </c>
+      <c r="N32" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" customHeight="1">
+      <c r="A33" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F33" s="42"/>
+      <c r="H33" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="I33" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="J33" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K33" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="M33" s="42">
+        <f>countif(Table2[[to]:[from]],I33)</f>
+        <v>5</v>
+      </c>
+      <c r="N33" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" customHeight="1">
+      <c r="A34" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F34" s="42"/>
+      <c r="H34" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="J34" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K34" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="M34" s="42">
+        <f>countif(Table2[[to]:[from]],I34)</f>
+        <v>3</v>
+      </c>
+      <c r="N34" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="22.5" customHeight="1">
+      <c r="A35" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F35" s="42"/>
+      <c r="H35" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="J35" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K35" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="M35" s="42">
+        <f>countif(Table2[[to]:[from]],I35)</f>
+        <v>4</v>
+      </c>
+      <c r="N35" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" ht="22.5" customHeight="1">
+      <c r="A36" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F36" s="42"/>
+      <c r="H36" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="J36" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K36" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L36" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M36" s="42">
+        <f>countif(Table2[[to]:[from]],I36)</f>
+        <v>7</v>
+      </c>
+      <c r="N36" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" customHeight="1">
+      <c r="A37" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D37" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F37" s="42"/>
+      <c r="H37" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I37" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="J37" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="K37" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L37" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M37" s="42">
+        <f>countif(Table2[[to]:[from]],I37)</f>
+        <v>8</v>
+      </c>
+      <c r="N37" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" ht="22.5" customHeight="1">
+      <c r="A38" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F38" s="42"/>
+      <c r="H38" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I38" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="J38" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="K38" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L38" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="M38" s="42">
+        <f>countif(Table2[[to]:[from]],I38)</f>
+        <v>4</v>
+      </c>
+      <c r="N38" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" ht="22.5" customHeight="1">
+      <c r="A39" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F39" s="42"/>
+      <c r="H39" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I39" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="J39" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="K39" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L39" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M39" s="42">
+        <f>countif(Table2[[to]:[from]],I39)</f>
+        <v>8</v>
+      </c>
+      <c r="N39" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" ht="22.5" customHeight="1">
+      <c r="A40" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E40" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F40" s="42"/>
+      <c r="H40" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I40" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="J40" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="K40" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L40" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M40" s="42">
+        <f>countif(Table2[[to]:[from]],I40)</f>
+        <v>8</v>
+      </c>
+      <c r="N40" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" ht="22.5" customHeight="1">
+      <c r="A41" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="42"/>
+      <c r="H41" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I41" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="J41" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="K41" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L41" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="M41" s="42">
+        <f>countif(Table2[[to]:[from]],I41)</f>
+        <v>5</v>
+      </c>
+      <c r="N41" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" ht="22.5" customHeight="1">
+      <c r="A42" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D42" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E42" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F42" s="42"/>
+      <c r="H42" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I42" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J42" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="K42" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L42" s="26">
+        <v>9.0</v>
+      </c>
+      <c r="M42" s="42">
+        <f>countif(Table2[[to]:[from]],I42)</f>
+        <v>9</v>
+      </c>
+      <c r="N42" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" ht="22.5" customHeight="1">
+      <c r="A43" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E43" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F43" s="42"/>
+      <c r="H43" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I43" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="J43" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="K43" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L43" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M43" s="42">
+        <f>countif(Table2[[to]:[from]],I43)</f>
+        <v>8</v>
+      </c>
+      <c r="N43" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="A44" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F44" s="42"/>
+      <c r="H44" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I44" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="J44" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="K44" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L44" s="26">
+        <v>9.0</v>
+      </c>
+      <c r="M44" s="42">
+        <f>countif(Table2[[to]:[from]],I44)</f>
+        <v>9</v>
+      </c>
+      <c r="N44" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E45" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F45" s="42"/>
+      <c r="H45" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I45" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="J45" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K45" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L45" s="26">
+        <v>6.0</v>
+      </c>
+      <c r="M45" s="42">
+        <f>countif(Table2[[to]:[from]],I45)</f>
+        <v>6</v>
+      </c>
+      <c r="N45" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" customHeight="1">
+      <c r="A46" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D46" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F46" s="42"/>
+      <c r="H46" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I46" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="J46" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="K46" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L46" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M46" s="42">
+        <f>countif(Table2[[to]:[from]],I46)</f>
+        <v>8</v>
+      </c>
+      <c r="N46" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" ht="22.5" customHeight="1">
+      <c r="A47" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F47" s="42"/>
+      <c r="H47" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I47" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="J47" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="K47" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L47" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="M47" s="42">
+        <f>countif(Table2[[to]:[from]],I47)</f>
+        <v>5</v>
+      </c>
+      <c r="N47" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" ht="22.5" customHeight="1">
+      <c r="A48" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F48" s="42"/>
+      <c r="H48" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I48" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J48" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="K48" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L48" s="26">
+        <v>9.0</v>
+      </c>
+      <c r="M48" s="42">
+        <f>countif(Table2[[to]:[from]],I48)</f>
+        <v>9</v>
+      </c>
+      <c r="N48" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" ht="22.5" customHeight="1">
+      <c r="A49" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F49" s="42"/>
+      <c r="H49" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="I49" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="J49" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="K49" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L49" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="M49" s="42">
+        <f>countif(Table2[[to]:[from]],I49)</f>
+        <v>5</v>
+      </c>
+      <c r="N49" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" ht="22.5" customHeight="1">
+      <c r="A50" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" s="23">
+        <v>2.0</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="F50" s="42"/>
+      <c r="H50" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="I50" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="J50" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="K50" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L50" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M50" s="42">
+        <f>countif(Table2[[to]:[from]],I50)</f>
+        <v>7</v>
+      </c>
+      <c r="N50" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="A51" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="23">
+        <v>3.0</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="F51" s="42"/>
+      <c r="H51" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="I51" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="J51" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K51" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L51" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="M51" s="42">
+        <f>countif(Table2[[to]:[from]],I51)</f>
+        <v>2</v>
+      </c>
+      <c r="N51" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D52" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="F52" s="42"/>
+      <c r="H52" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="I52" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="J52" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="K52" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L52" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M52" s="42">
+        <f>countif(Table2[[to]:[from]],I52)</f>
+        <v>7</v>
+      </c>
+      <c r="N52" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D53" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="F53" s="42"/>
+      <c r="H53" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="I53" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="J53" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K53" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L53" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="M53" s="42">
+        <f>countif(Table2[[to]:[from]],I53)</f>
+        <v>5</v>
+      </c>
+      <c r="N53" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D54" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E54" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F54" s="42"/>
+      <c r="H54" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="I54" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="J54" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K54" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L54" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="M54" s="42">
+        <f>countif(Table2[[to]:[from]],I54)</f>
+        <v>4</v>
+      </c>
+      <c r="N54" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E55" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F55" s="42"/>
+      <c r="H55" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="J55" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K55" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L55" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="M55" s="42">
+        <f>countif(Table2[[to]:[from]],I55)</f>
+        <v>4</v>
+      </c>
+      <c r="N55" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" ht="22.5" customHeight="1">
+      <c r="A56" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E56" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F56" s="42"/>
+      <c r="H56" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J56" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K56" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L56" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="M56" s="42">
+        <f>countif(Table2[[to]:[from]],I56)</f>
+        <v>3</v>
+      </c>
+      <c r="N56" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="A57" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D57" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E57" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F57" s="42"/>
+      <c r="H57" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="J57" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="K57" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L57" s="26">
+        <v>9.0</v>
+      </c>
+      <c r="M57" s="42">
+        <f>countif(Table2[[to]:[from]],I57)</f>
+        <v>9</v>
+      </c>
+      <c r="N57" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" ht="22.5" customHeight="1">
+      <c r="A58" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D58" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E58" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F58" s="42"/>
+      <c r="H58" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="J58" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K58" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L58" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="M58" s="42">
+        <f>countif(Table2[[to]:[from]],I58)</f>
+        <v>3</v>
+      </c>
+      <c r="N58" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" ht="22.5" customHeight="1">
+      <c r="A59" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E59" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F59" s="42"/>
+      <c r="H59" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="J59" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K59" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L59" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="M59" s="42">
+        <f>countif(Table2[[to]:[from]],I59)</f>
+        <v>4</v>
+      </c>
+      <c r="N59" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" ht="22.5" customHeight="1">
+      <c r="A60" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E60" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F60" s="42"/>
+      <c r="H60" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I60" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="J60" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K60" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L60" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="M60" s="42">
+        <f>countif(Table2[[to]:[from]],I60)</f>
+        <v>5</v>
+      </c>
+      <c r="N60" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" ht="22.5" customHeight="1">
+      <c r="A61" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C61" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E61" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F61" s="42"/>
+      <c r="H61" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="J61" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="K61" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="L61" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M61" s="42">
+        <f>countif(Table2[[to]:[from]],I61)</f>
+        <v>7</v>
+      </c>
+      <c r="N61" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" ht="22.5" customHeight="1">
+      <c r="A62" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E62" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F62" s="42"/>
+      <c r="H62" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I62" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="J62" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K62" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L62" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="M62" s="42">
+        <f>countif(Table2[[to]:[from]],I62)</f>
+        <v>5</v>
+      </c>
+      <c r="N62" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" ht="22.5" customHeight="1">
+      <c r="A63" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D63" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E63" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F63" s="42"/>
+      <c r="H63" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I63" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J63" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K63" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L63" s="26">
+        <v>7.0</v>
+      </c>
+      <c r="M63" s="42">
+        <f>countif(Table2[[to]:[from]],I63)</f>
+        <v>7</v>
+      </c>
+      <c r="N63" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" ht="22.5" customHeight="1">
+      <c r="A64" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D64" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E64" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F64" s="42"/>
+      <c r="H64" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I64" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J64" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="K64" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="L64" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="M64" s="42">
+        <f>countif(Table2[[to]:[from]],I64)</f>
+        <v>8</v>
+      </c>
+      <c r="N64" s="42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" ht="22.5" customHeight="1">
+      <c r="A65" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C65" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D65" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E65" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="F65" s="42"/>
+    </row>
+    <row r="66" ht="22.5" customHeight="1">
+      <c r="A66" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D66" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E66" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F66" s="42"/>
+    </row>
+    <row r="67" ht="22.5" customHeight="1">
+      <c r="A67" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C67" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D67" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E67" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F67" s="42"/>
+    </row>
+    <row r="68" ht="22.5" customHeight="1">
+      <c r="A68" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D68" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E68" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F68" s="42"/>
+    </row>
+    <row r="69" ht="22.5" customHeight="1">
+      <c r="A69" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D69" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E69" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F69" s="42"/>
+    </row>
+    <row r="70" ht="22.5" customHeight="1">
+      <c r="A70" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E70" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F70" s="42"/>
+    </row>
+    <row r="71" ht="22.5" customHeight="1">
+      <c r="A71" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D71" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="E71" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F71" s="42"/>
+    </row>
+    <row r="72" ht="22.5" customHeight="1">
+      <c r="A72" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D72" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E72" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F72" s="42"/>
+    </row>
+    <row r="73" ht="22.5" customHeight="1">
+      <c r="A73" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D73" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E73" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F73" s="42"/>
+    </row>
+    <row r="74" ht="22.5" customHeight="1">
+      <c r="A74" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C74" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E74" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F74" s="42"/>
+    </row>
+    <row r="75" ht="22.5" customHeight="1">
+      <c r="A75" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E75" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F75" s="42"/>
+    </row>
+    <row r="76" ht="22.5" customHeight="1">
+      <c r="A76" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B76" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D76" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E76" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F76" s="42"/>
+    </row>
+    <row r="77" ht="22.5" customHeight="1">
+      <c r="A77" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B77" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C77" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D77" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E77" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F77" s="42"/>
+    </row>
+    <row r="78" ht="22.5" customHeight="1">
+      <c r="A78" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B78" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C78" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D78" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="E78" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F78" s="42"/>
+    </row>
+    <row r="79" ht="22.5" customHeight="1">
+      <c r="A79" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D79" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E79" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F79" s="42"/>
+    </row>
+    <row r="80" ht="22.5" customHeight="1">
+      <c r="A80" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E80" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F80" s="42"/>
+    </row>
+    <row r="81" ht="22.5" customHeight="1">
+      <c r="A81" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C81" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D81" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E81" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F81" s="42"/>
+    </row>
+    <row r="82" ht="22.5" customHeight="1">
+      <c r="A82" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B82" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C82" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D82" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E82" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F82" s="42"/>
+    </row>
+    <row r="83" ht="22.5" customHeight="1">
+      <c r="A83" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B83" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C83" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D83" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E83" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F83" s="42"/>
+    </row>
+    <row r="84" ht="22.5" customHeight="1">
+      <c r="A84" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C84" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D84" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E84" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F84" s="42"/>
+    </row>
+    <row r="85" ht="22.5" customHeight="1">
+      <c r="A85" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B85" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C85" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D85" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E85" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F85" s="42"/>
+    </row>
+    <row r="86" ht="22.5" customHeight="1">
+      <c r="A86" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C86" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D86" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E86" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F86" s="42"/>
+    </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="A87" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B87" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C87" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D87" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E87" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F87" s="42"/>
+    </row>
+    <row r="88" ht="22.5" customHeight="1">
+      <c r="A88" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B88" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D88" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E88" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F88" s="42"/>
+    </row>
+    <row r="89" ht="22.5" customHeight="1">
+      <c r="A89" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B89" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C89" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D89" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E89" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F89" s="42"/>
+    </row>
+    <row r="90" ht="22.5" customHeight="1">
+      <c r="A90" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B90" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C90" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D90" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E90" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F90" s="42"/>
+    </row>
+    <row r="91" ht="22.5" customHeight="1">
+      <c r="A91" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B91" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C91" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D91" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E91" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F91" s="42"/>
+    </row>
+    <row r="92" ht="22.5" customHeight="1">
+      <c r="A92" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B92" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C92" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D92" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E92" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F92" s="42"/>
+    </row>
+    <row r="93" ht="22.5" customHeight="1">
+      <c r="A93" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B93" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C93" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E93" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F93" s="42"/>
+    </row>
+    <row r="94" ht="22.5" customHeight="1">
+      <c r="A94" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B94" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C94" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D94" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E94" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F94" s="42"/>
+    </row>
+    <row r="95" ht="22.5" customHeight="1">
+      <c r="A95" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B95" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D95" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E95" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F95" s="42"/>
+    </row>
+    <row r="96" ht="22.5" customHeight="1">
+      <c r="A96" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B96" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C96" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="D96" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E96" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F96" s="42"/>
+    </row>
+    <row r="97" ht="22.5" customHeight="1">
+      <c r="A97" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B97" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="C97" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D97" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E97" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F97" s="42"/>
+    </row>
+    <row r="98" ht="22.5" customHeight="1">
+      <c r="A98" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B98" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="C98" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D98" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E98" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F98" s="42"/>
+    </row>
+    <row r="99" ht="22.5" customHeight="1">
+      <c r="A99" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B99" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="C99" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D99" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E99" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F99" s="42"/>
+    </row>
+    <row r="100" ht="22.5" customHeight="1">
+      <c r="A100" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B100" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="C100" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D100" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E100" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F100" s="42"/>
+    </row>
+    <row r="101" ht="22.5" customHeight="1">
+      <c r="A101" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B101" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="C101" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D101" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E101" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F101" s="42"/>
+    </row>
+    <row r="102" ht="22.5" customHeight="1">
+      <c r="A102" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B102" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C102" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D102" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E102" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F102" s="42"/>
+    </row>
+    <row r="103" ht="22.5" customHeight="1">
+      <c r="A103" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B103" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C103" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D103" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E103" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F103" s="42"/>
+    </row>
+    <row r="104" ht="22.5" customHeight="1">
+      <c r="A104" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B104" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C104" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D104" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E104" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F104" s="42"/>
+    </row>
+    <row r="105" ht="22.5" customHeight="1">
+      <c r="A105" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B105" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C105" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D105" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E105" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F105" s="42"/>
+    </row>
+    <row r="106" ht="22.5" customHeight="1">
+      <c r="A106" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B106" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C106" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D106" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E106" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F106" s="42"/>
+    </row>
+    <row r="107" ht="22.5" customHeight="1">
+      <c r="A107" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B107" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C107" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D107" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E107" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F107" s="42"/>
+    </row>
+    <row r="108" ht="22.5" customHeight="1">
+      <c r="A108" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B108" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C108" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D108" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E108" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F108" s="42"/>
+    </row>
+    <row r="109" ht="22.5" customHeight="1">
+      <c r="A109" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B109" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C109" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D109" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E109" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F109" s="42"/>
+    </row>
+    <row r="110" ht="22.5" customHeight="1">
+      <c r="A110" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B110" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C110" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D110" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E110" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F110" s="42"/>
+    </row>
+    <row r="111" ht="22.5" customHeight="1">
+      <c r="A111" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B111" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C111" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D111" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E111" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F111" s="42"/>
+    </row>
+    <row r="112" ht="22.5" customHeight="1">
+      <c r="A112" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B112" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C112" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D112" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E112" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F112" s="42"/>
+    </row>
+    <row r="113" ht="22.5" customHeight="1">
+      <c r="A113" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B113" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C113" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D113" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E113" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F113" s="42"/>
+    </row>
+    <row r="114" ht="22.5" customHeight="1">
+      <c r="A114" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B114" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C114" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D114" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E114" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F114" s="42"/>
+    </row>
+    <row r="115" ht="22.5" customHeight="1">
+      <c r="A115" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B115" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C115" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D115" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="E115" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F115" s="42"/>
+    </row>
+    <row r="116" ht="22.5" customHeight="1">
+      <c r="A116" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B116" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C116" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D116" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E116" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F116" s="42"/>
+    </row>
+    <row r="117" ht="22.5" customHeight="1">
+      <c r="A117" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B117" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C117" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D117" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="E117" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="F117" s="42"/>
+    </row>
+    <row r="118" ht="22.5" customHeight="1">
+      <c r="A118" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B118" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C118" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D118" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E118" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F118" s="42"/>
+    </row>
+    <row r="119" ht="22.5" customHeight="1">
+      <c r="A119" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B119" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C119" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D119" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E119" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F119" s="42"/>
+    </row>
+    <row r="120" ht="22.5" customHeight="1">
+      <c r="A120" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B120" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C120" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D120" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E120" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F120" s="42"/>
+    </row>
+    <row r="121" ht="22.5" customHeight="1">
+      <c r="A121" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B121" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C121" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D121" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E121" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F121" s="42"/>
+    </row>
+    <row r="122" ht="22.5" customHeight="1">
+      <c r="A122" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B122" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C122" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D122" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E122" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F122" s="42"/>
+    </row>
+    <row r="123" ht="22.5" customHeight="1">
+      <c r="A123" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B123" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C123" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D123" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E123" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F123" s="42"/>
+    </row>
+    <row r="124" ht="22.5" customHeight="1">
+      <c r="A124" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B124" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C124" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D124" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E124" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F124" s="42"/>
+    </row>
+    <row r="125" ht="22.5" customHeight="1">
+      <c r="A125" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B125" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C125" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E125" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F125" s="42"/>
+    </row>
+    <row r="126" ht="22.5" customHeight="1">
+      <c r="A126" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B126" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C126" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D126" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E126" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F126" s="42"/>
+    </row>
+    <row r="127" ht="22.5" customHeight="1">
+      <c r="A127" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B127" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C127" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D127" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E127" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F127" s="42"/>
+    </row>
+    <row r="128" ht="22.5" customHeight="1">
+      <c r="A128" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B128" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C128" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D128" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E128" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F128" s="42"/>
+    </row>
+    <row r="129" ht="22.5" customHeight="1">
+      <c r="A129" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B129" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C129" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D129" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E129" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F129" s="42"/>
+    </row>
+    <row r="130" ht="22.5" customHeight="1">
+      <c r="A130" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B130" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C130" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D130" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E130" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F130" s="42"/>
+    </row>
+    <row r="131" ht="22.5" customHeight="1">
+      <c r="A131" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B131" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C131" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D131" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E131" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F131" s="42"/>
+    </row>
+    <row r="132" ht="22.5" customHeight="1">
+      <c r="A132" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B132" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C132" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D132" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E132" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F132" s="42"/>
+    </row>
+    <row r="133" ht="22.5" customHeight="1">
+      <c r="A133" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B133" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C133" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D133" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E133" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F133" s="42"/>
+    </row>
+    <row r="134" ht="22.5" customHeight="1">
+      <c r="A134" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B134" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C134" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D134" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E134" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F134" s="42"/>
+    </row>
+    <row r="135" ht="22.5" customHeight="1">
+      <c r="A135" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B135" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C135" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D135" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E135" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F135" s="42"/>
+    </row>
+    <row r="136" ht="22.5" customHeight="1">
+      <c r="A136" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B136" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C136" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D136" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="E136" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="F136" s="42"/>
+    </row>
+    <row r="137" ht="22.5" customHeight="1">
+      <c r="A137" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B137" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C137" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D137" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="E137" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F137" s="42"/>
+    </row>
+    <row r="138" ht="22.5" customHeight="1">
+      <c r="A138" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B138" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C138" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D138" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E138" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F138" s="42"/>
+    </row>
+    <row r="139" ht="22.5" customHeight="1">
+      <c r="A139" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B139" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C139" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D139" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E139" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F139" s="42"/>
+    </row>
+    <row r="140" ht="22.5" customHeight="1">
+      <c r="A140" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B140" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C140" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D140" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E140" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F140" s="42"/>
+    </row>
+    <row r="141" ht="22.5" customHeight="1">
+      <c r="A141" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B141" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C141" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="D141" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E141" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F141" s="42"/>
+    </row>
+    <row r="142" ht="22.5" customHeight="1">
+      <c r="A142" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B142" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C142" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D142" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E142" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F142" s="42"/>
+    </row>
+    <row r="143" ht="22.5" customHeight="1">
+      <c r="A143" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B143" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C143" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D143" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E143" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F143" s="42"/>
+    </row>
+    <row r="144" ht="22.5" customHeight="1">
+      <c r="A144" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B144" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C144" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D144" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E144" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F144" s="42"/>
+    </row>
+    <row r="145" ht="22.5" customHeight="1">
+      <c r="A145" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B145" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C145" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D145" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E145" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F145" s="42"/>
+    </row>
+    <row r="146" ht="22.5" customHeight="1">
+      <c r="A146" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B146" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C146" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D146" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E146" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F146" s="42"/>
+    </row>
+    <row r="147" ht="22.5" customHeight="1">
+      <c r="A147" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B147" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C147" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D147" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E147" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F147" s="42"/>
+    </row>
+    <row r="148" ht="22.5" customHeight="1">
+      <c r="A148" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B148" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C148" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D148" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="E148" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F148" s="42"/>
+    </row>
+    <row r="149" ht="22.5" customHeight="1">
+      <c r="A149" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B149" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C149" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D149" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E149" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F149" s="42"/>
+    </row>
+    <row r="150" ht="22.5" customHeight="1">
+      <c r="A150" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B150" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C150" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D150" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E150" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F150" s="42"/>
+    </row>
+    <row r="151" ht="22.5" customHeight="1">
+      <c r="A151" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B151" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C151" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D151" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E151" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F151" s="42"/>
+    </row>
+    <row r="152" ht="22.5" customHeight="1">
+      <c r="A152" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B152" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C152" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D152" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E152" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F152" s="42"/>
+    </row>
+    <row r="153" ht="22.5" customHeight="1">
+      <c r="A153" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B153" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C153" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E153" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="F153" s="42"/>
+    </row>
+    <row r="154" ht="22.5" customHeight="1">
+      <c r="A154" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B154" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C154" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D154" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E154" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F154" s="42"/>
+    </row>
+    <row r="155" ht="22.5" customHeight="1">
+      <c r="A155" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B155" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C155" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D155" s="26">
+        <v>6.0</v>
+      </c>
+      <c r="E155" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F155" s="42"/>
+    </row>
+    <row r="156" ht="22.5" customHeight="1">
+      <c r="A156" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B156" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C156" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D156" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E156" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F156" s="26"/>
+    </row>
+    <row r="157" ht="22.5" customHeight="1">
+      <c r="A157" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B157" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C157" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D157" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E157" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F157" s="26"/>
+    </row>
+    <row r="158" ht="22.5" customHeight="1">
+      <c r="A158" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B158" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C158" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D158" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E158" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F158" s="26">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="159" ht="22.5" customHeight="1">
+      <c r="A159" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B159" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C159" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D159" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E159" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F159" s="26">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="160" ht="22.5" customHeight="1">
+      <c r="A160" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B160" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C160" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D160" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E160" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F160" s="26">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="161" ht="22.5" customHeight="1">
+      <c r="A161" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B161" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C161" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D161" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E161" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F161" s="26">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="162" ht="22.5" customHeight="1">
+      <c r="A162" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B162" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C162" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D162" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E162" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="F162" s="26"/>
+    </row>
+    <row r="163" ht="22.5" customHeight="1">
+      <c r="A163" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B163" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C163" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D163" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E163" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F163" s="26">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="164" ht="22.5" customHeight="1">
+      <c r="A164" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B164" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C164" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D164" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E164" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F164" s="26">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="165" ht="22.5" customHeight="1">
+      <c r="A165" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B165" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C165" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D165" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="E165" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F165" s="26">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="166" ht="22.5" customHeight="1">
+      <c r="A166" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B166" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C166" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D166" s="26">
+        <v>5.0</v>
+      </c>
+      <c r="E166" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F166" s="26">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="167" ht="22.5" customHeight="1">
+      <c r="A167" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B167" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C167" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="D167" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E167" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F167" s="26">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="168" ht="22.5" customHeight="1">
+      <c r="A168" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B168" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C168" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="D168" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E168" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F168" s="26">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="169" ht="22.5" customHeight="1">
+      <c r="A169" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B169" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C169" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D169" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E169" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F169" s="26">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="170" ht="22.5" customHeight="1">
+      <c r="A170" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B170" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C170" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D170" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E170" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F170" s="26">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="171" ht="22.5" customHeight="1">
+      <c r="A171" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B171" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C171" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D171" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E171" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F171" s="26">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="172" ht="22.5" customHeight="1">
+      <c r="A172" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B172" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C172" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D172" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E172" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F172" s="26">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="173" ht="22.5" customHeight="1">
+      <c r="A173" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B173" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C173" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D173" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E173" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F173" s="26">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="174" ht="22.5" customHeight="1">
+      <c r="A174" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B174" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C174" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D174" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E174" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="F174" s="26"/>
+    </row>
+    <row r="175" ht="22.5" customHeight="1">
+      <c r="A175" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B175" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C175" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D175" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E175" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F175" s="26">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="176" ht="22.5" customHeight="1">
+      <c r="A176" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B176" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C176" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D176" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E176" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F176" s="26"/>
+    </row>
+    <row r="177" ht="22.5" customHeight="1">
+      <c r="A177" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B177" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C177" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D177" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E177" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F177" s="26"/>
+    </row>
+    <row r="178" ht="22.5" customHeight="1">
+      <c r="A178" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B178" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C178" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D178" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E178" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F178" s="26"/>
+    </row>
+    <row r="179" ht="22.5" customHeight="1">
+      <c r="A179" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B179" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C179" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D179" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E179" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F179" s="26"/>
+    </row>
+    <row r="180" ht="22.5" customHeight="1">
+      <c r="A180" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B180" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C180" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D180" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E180" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F180" s="26"/>
+    </row>
+    <row r="181" ht="22.5" customHeight="1">
+      <c r="A181" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B181" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C181" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="D181" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E181" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F181" s="26"/>
+    </row>
+    <row r="182" ht="22.5" customHeight="1">
+      <c r="A182" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B182" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="C182" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D182" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E182" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F182" s="26"/>
+    </row>
+    <row r="183" ht="22.5" customHeight="1">
+      <c r="A183" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B183" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="C183" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D183" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E183" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F183" s="26"/>
+    </row>
+    <row r="184" ht="22.5" customHeight="1">
+      <c r="A184" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B184" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C184" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D184" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E184" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F184" s="26"/>
+    </row>
+    <row r="185" ht="22.5" customHeight="1">
+      <c r="A185" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B185" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C185" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D185" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E185" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F185" s="26"/>
+    </row>
+    <row r="186" ht="22.5" customHeight="1">
+      <c r="A186" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B186" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C186" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D186" s="26">
+        <v>6.0</v>
+      </c>
+      <c r="E186" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F186" s="26"/>
+    </row>
+    <row r="187" ht="22.5" customHeight="1">
+      <c r="A187" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B187" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C187" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D187" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E187" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F187" s="26"/>
+    </row>
+    <row r="188" ht="22.5" customHeight="1">
+      <c r="A188" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B188" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C188" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D188" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E188" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F188" s="26"/>
+    </row>
+    <row r="189" ht="22.5" customHeight="1">
+      <c r="A189" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B189" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C189" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D189" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E189" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F189" s="26"/>
+    </row>
+    <row r="190" ht="22.5" customHeight="1">
+      <c r="A190" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B190" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C190" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D190" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E190" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F190" s="26"/>
+    </row>
+    <row r="191" ht="22.5" customHeight="1">
+      <c r="A191" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B191" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C191" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D191" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E191" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F191" s="26"/>
+    </row>
+    <row r="192" ht="22.5" customHeight="1">
+      <c r="A192" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B192" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C192" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D192" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E192" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F192" s="26"/>
+    </row>
+    <row r="193" ht="22.5" customHeight="1">
+      <c r="A193" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B193" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C193" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D193" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E193" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F193" s="26"/>
+    </row>
+    <row r="194" ht="22.5" customHeight="1">
+      <c r="A194" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B194" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C194" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D194" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="E194" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F194" s="26"/>
+    </row>
+    <row r="195" ht="22.5" customHeight="1">
+      <c r="A195" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B195" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C195" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D195" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E195" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F195" s="26"/>
+    </row>
+    <row r="196" ht="22.5" customHeight="1">
+      <c r="A196" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B196" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C196" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D196" s="26">
+        <v>4.0</v>
+      </c>
+      <c r="E196" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F196" s="26"/>
+    </row>
+    <row r="197" ht="22.5" customHeight="1">
+      <c r="A197" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B197" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C197" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D197" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E197" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F197" s="26"/>
+    </row>
+    <row r="198" ht="22.5" customHeight="1">
+      <c r="A198" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B198" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C198" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D198" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="E198" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F198" s="26"/>
+    </row>
+    <row r="199" ht="22.5" customHeight="1">
+      <c r="A199" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B199" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C199" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D199" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E199" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F199" s="26"/>
+    </row>
+    <row r="200" ht="22.5" customHeight="1">
+      <c r="A200" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B200" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C200" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D200" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E200" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F200" s="26"/>
+    </row>
+    <row r="201" ht="22.5" customHeight="1">
+      <c r="A201" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B201" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C201" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D201" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="E201" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F201" s="26"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
